--- a/test/client.xlsx
+++ b/test/client.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C742C660-2445-4E91-9ACD-1761B1A9F56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D93DD63-90A6-4D44-BDED-44F3FF65829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>file3</t>
   </si>
   <si>
-    <t>ABC Pvt Ltd</t>
-  </si>
-  <si>
     <t>private ltd</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>active</t>
   </si>
   <si>
-    <t>pan</t>
-  </si>
-  <si>
     <t>abc123</t>
   </si>
   <si>
@@ -110,6 +104,12 @@
   </si>
   <si>
     <t>pass@123</t>
+  </si>
+  <si>
+    <t>tan</t>
+  </si>
+  <si>
+    <t>XYZ Pvt Ltd</t>
   </si>
 </sst>
 </file>
@@ -541,19 +541,19 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
       </c>
       <c r="F2">
         <v>9876543210</v>
@@ -562,34 +562,34 @@
         <v>9876543211</v>
       </c>
       <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/test/client.xlsx
+++ b/test/client.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D93DD63-90A6-4D44-BDED-44F3FF65829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E02B4A3-69CE-4632-A3D4-9FE7136E7E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>client_name</t>
   </si>
@@ -109,14 +109,17 @@
     <t>tan</t>
   </si>
   <si>
-    <t>XYZ Pvt Ltd</t>
+    <t>ccccccc</t>
+  </si>
+  <si>
+    <t>DDDDDD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +136,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -483,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -592,9 +601,71 @@
         <v>26</v>
       </c>
     </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>9876543210</v>
+      </c>
+      <c r="G3">
+        <v>9876543211</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M5" s="2"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{8190B578-5F48-4977-9C1B-0947CEC807F3}"/>
+    <hyperlink ref="M3:M5" r:id="rId1" display="pass@123" xr:uid="{EA285200-2460-48E8-8A75-76E95EE5AB6B}"/>
+    <hyperlink ref="M2" r:id="rId2" xr:uid="{8190B578-5F48-4977-9C1B-0947CEC807F3}"/>
+    <hyperlink ref="M3" r:id="rId3" xr:uid="{2BABFE91-7D5B-45A7-96E2-AB2CD435C4A5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
